--- a/products/Editors/scenarios/smoke/7. Предпросмотр печати и печать .docx.xlsx
+++ b/products/Editors/scenarios/smoke/7. Предпросмотр печати и печать .docx.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Editors\test_cases\smoke\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Testing\products\Editors\scenarios\smoke\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CA4277-8D22-4BB0-92D5-4E2B95073C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B0BB8C-5BE4-4FE2-A8E5-1AB4525F6581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="28">
   <si>
     <t>Расположение</t>
   </si>
@@ -61,15 +61,6 @@
   </si>
   <si>
     <t>smoke</t>
-  </si>
-  <si>
-    <t>Установка и обновление</t>
-  </si>
-  <si>
-    <t>Успешно пройдены</t>
-  </si>
-  <si>
-    <t>Открыт документ “Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.docx“</t>
   </si>
   <si>
     <t>Масштаб документа изменён установлен “По размеру страницы“.
@@ -77,65 +68,71 @@
 Отображается 4-й лист.</t>
   </si>
   <si>
-    <t>Кликнуть по кнопке “Напечатать файл”.</t>
+    <t>Блок “Принтер”.
+Если в выпадающем списке установлено значение “Печатать в файл”, то этот шаг пропустить.</t>
+  </si>
+  <si>
+    <t>В выпадающем списке установить значение “Печатать в файл”.</t>
+  </si>
+  <si>
+    <t>Нажать кнопку “Печать”.</t>
+  </si>
+  <si>
+    <t>Нажать клавишу “Enter”.</t>
+  </si>
+  <si>
+    <t>Системное окно проводника закрыто.
+Документ сохранен.</t>
+  </si>
+  <si>
+    <t>Файл Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.pdf существует.</t>
+  </si>
+  <si>
+    <t>Вкладки закрыты.
+Отображается главное окно редактора.</t>
+  </si>
+  <si>
+    <t>Очистить список последних файлов.</t>
+  </si>
+  <si>
+    <t>Список очищен.</t>
+  </si>
+  <si>
+    <t>Окно редактора закрыто.</t>
+  </si>
+  <si>
+    <t>Тест кейс 6. Открытие файла эталона .docx успешно пройден
+Открыт документ “Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.docx“</t>
+  </si>
+  <si>
+    <t>Кликнуть по кнопке “Напечатать файл”.
+&lt;use href="#btn-print" class="zoom-int"&gt;&lt;/use&gt;</t>
   </si>
   <si>
     <t>Открылось меню печати.
 В области предварительного просмотра отображается первая страница документа.
-В счетчике страниц указано количество: 1 из 4.</t>
-  </si>
-  <si>
-    <t>Блок “Принтер”.
-Если в выпадающем списке установлено значение “Печатать в файл”, то этот шаг пропустить.</t>
-  </si>
-  <si>
-    <t>В выпадающем списке установить значение “Печатать в файл”.</t>
-  </si>
-  <si>
-    <t>Нажать кнопку “Печать”.</t>
-  </si>
-  <si>
-    <t>Нажать клавишу “Enter”.</t>
-  </si>
-  <si>
-    <t>Системное окно проводника закрыто.
-Документ сохранен.</t>
-  </si>
-  <si>
-    <t>Файл Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.pdf существует.</t>
-  </si>
-  <si>
-    <t>Вкладки закрыты.
-Отображается главное окно редактора.</t>
-  </si>
-  <si>
-    <t>Очистить список последних файлов.</t>
-  </si>
-  <si>
-    <t>Список очищен.</t>
-  </si>
-  <si>
-    <t>Окно редактора закрыто.</t>
+В счетчике страниц указано количество: 1 из 4.
+&lt;div id="print-number-page"&gt; = &lt;label id="print-count-page"&gt;</t>
   </si>
   <si>
     <t>Открыто системное окно проводника.
 По умолчанию путь сохранения
 Mac: /Users/mario/Documents/
-Windows: С:\Users\HP\Documents\
+Windows: С:\Users\Users\Documents\
 Linux: home/mario/Документы/
 Имя документа Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora без указания формата.</t>
   </si>
   <si>
     <t>Проверить наличие сохраненного документа
 Mac: Users/mario/Документы/Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.pdf
-Windows: С:\Users\HP\Documents\Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.pdf
+Windows: С:\Users\Users\Documents\Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.pdf
 Linux: /home/mario/Документы/Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.pdf</t>
   </si>
   <si>
-    <t>Закрыть вкладки документов без сохранения нажатием на “X“ в верхнем правом углу.</t>
-  </si>
-  <si>
-    <t>Закрыть редактор нажав на “X“ в верхнем правом углу.</t>
+    <t>Закрыть вкладки документов без сохранения нажатием на “X“ в верхнем правом углу вкладки документа.</t>
+  </si>
+  <si>
+    <t>Закрыть редактор нажав на “X“ в верхнем правом углу главного окна редактора.</t>
   </si>
 </sst>
 </file>
@@ -553,53 +550,48 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -609,14 +601,14 @@
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>8</v>
@@ -633,13 +625,13 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>8</v>
@@ -656,13 +648,13 @@
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>8</v>
@@ -679,13 +671,13 @@
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>8</v>
@@ -702,13 +694,13 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>8</v>
@@ -728,10 +720,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>8</v>
@@ -751,10 +743,10 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>8</v>
@@ -774,10 +766,10 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>8</v>
